--- a/agent-3/db/test_dashboard_output.xlsx
+++ b/agent-3/db/test_dashboard_output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://parkar-my.sharepoint.com/personal/aranjan_parkar_in/Documents/Desktop/redpinefinal/redpine-agents/agent-3/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FC701776EAD2BF32211302DBD6C91E294F1B6569" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C6DAA77E4E4E9D2141928ADAB63D82AE82FAABB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB008E4F-6FC6-4E8A-B2B7-79AAB717FA3F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Companies_DB!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dashboard!$A$28:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dashboard!$A$30:$K$30</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="128">
   <si>
     <t>Agent 3 - Business Acquisition Targeting Dashboard</t>
   </si>
@@ -40,10 +40,10 @@
     <t>Surface family-owned, founder-led businesses that fit the acquisition profile</t>
   </si>
   <si>
-    <t>FL, Florida</t>
-  </si>
-  <si>
-    <t>22-Jun-2026 04:14 PM</t>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>23-Jun-2026 11:15 AM</t>
   </si>
   <si>
     <t xml:space="preserve">  Founder-Led:  5</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">  Highest Score:  60</t>
   </si>
   <si>
-    <t xml:space="preserve">  New Today:  2</t>
+    <t xml:space="preserve">  New Today:  0</t>
   </si>
   <si>
     <t>🎯 Total Targets Found</t>
@@ -76,7 +76,7 @@
     <t>All Time</t>
   </si>
   <si>
-    <t>vs Last Week: ↓ 5</t>
+    <t>vs Last Week: ↓ 7</t>
   </si>
   <si>
     <t>vs Last Week: ↑ 1</t>
@@ -103,9 +103,6 @@
     <t>Key Insights</t>
   </si>
   <si>
-    <t>Florida</t>
-  </si>
-  <si>
     <t>20-40</t>
   </si>
   <si>
@@ -115,121 +112,115 @@
     <t>• 56% of targets are founder-led</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>40-60</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>60-80</t>
+  </si>
+  <si>
+    <t>Business Services &amp; Supp...</t>
+  </si>
+  <si>
+    <t>80-100</t>
+  </si>
+  <si>
+    <t>Residential Building Con...</t>
+  </si>
+  <si>
+    <t>• 44% of targets are family-owned</t>
+  </si>
+  <si>
+    <t>Venture Capital and Priv...</t>
+  </si>
+  <si>
+    <t>• Florida has the highest volume</t>
+  </si>
+  <si>
+    <t>• 0 new targets added this run</t>
+  </si>
+  <si>
+    <t>• 0 companies scored 80+</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Founder Name</t>
+  </si>
+  <si>
+    <t>Founder Age (Est.)</t>
+  </si>
+  <si>
+    <t>Years in Business</t>
+  </si>
+  <si>
+    <t>Readiness Score</t>
+  </si>
+  <si>
+    <t>Ownership Status</t>
+  </si>
+  <si>
+    <t>Ownership Tenure</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Why Selected</t>
+  </si>
+  <si>
+    <t>Arthrex</t>
+  </si>
+  <si>
+    <t>Reinhold Schmieding</t>
+  </si>
+  <si>
+    <t>Pursuing</t>
+  </si>
+  <si>
+    <t>Arthrex's long history and family ownership make it an appealing acquisition target.</t>
+  </si>
+  <si>
+    <t>American Sugar Refining</t>
+  </si>
+  <si>
+    <t>Florida Crystals Corporation and Sugar Cane Growers Cooperative of Florida</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Established food industry player with strong family ownership and partnership structure.</t>
+  </si>
+  <si>
+    <t>Acosta</t>
+  </si>
+  <si>
+    <t>L.T. Acosta</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Acosta's 99 years in business make it a stable acquisition target.</t>
+  </si>
+  <si>
+    <t>AG GENERAL CONTRACTOR</t>
+  </si>
+  <si>
+    <t>Guillermo Gaona and Pablo Allamand Sr.</t>
+  </si>
+  <si>
     <t>FL</t>
-  </si>
-  <si>
-    <t>40-60</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>60-80</t>
-  </si>
-  <si>
-    <t>Business Services &amp; Supp...</t>
-  </si>
-  <si>
-    <t>• 44% of targets are family-owned</t>
-  </si>
-  <si>
-    <t>80-100</t>
-  </si>
-  <si>
-    <t>Residential Building Con...</t>
-  </si>
-  <si>
-    <t>Venture Capital and Priv...</t>
-  </si>
-  <si>
-    <t>• Florida has the highest volume</t>
-  </si>
-  <si>
-    <t>• 2 new targets added this run</t>
-  </si>
-  <si>
-    <t>• 0 companies scored 80+</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Founder Name</t>
-  </si>
-  <si>
-    <t>Founder Age (Est.)</t>
-  </si>
-  <si>
-    <t>Years in Business</t>
-  </si>
-  <si>
-    <t>Readiness Score</t>
-  </si>
-  <si>
-    <t>Ownership Type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Why Selected</t>
-  </si>
-  <si>
-    <t>Arthrex</t>
-  </si>
-  <si>
-    <t>Reinhold Schmieding</t>
-  </si>
-  <si>
-    <t>Family-Owned, Founder-Led</t>
-  </si>
-  <si>
-    <t>Pursuing</t>
-  </si>
-  <si>
-    <t>Arthrex's long history and family ownership make it an appealing acquisition target.</t>
-  </si>
-  <si>
-    <t>American Sugar Refining</t>
-  </si>
-  <si>
-    <t>Florida Crystals Corporation and Sugar Cane Growers Cooperative of Florida</t>
-  </si>
-  <si>
-    <t>Family-Owned</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Established food industry player with strong family ownership and partnership structure.</t>
-  </si>
-  <si>
-    <t>Acosta</t>
-  </si>
-  <si>
-    <t>L.T. Acosta</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Acosta's 99 years in business make it a stable acquisition target.</t>
-  </si>
-  <si>
-    <t>AG GENERAL CONTRACTOR</t>
-  </si>
-  <si>
-    <t>Guillermo Gaona and Pablo Allamand Sr.</t>
-  </si>
-  <si>
-    <t>Founder-Led</t>
   </si>
   <si>
     <t>Established contractor with strong leadership and 46 years of industry experience.</t>
@@ -441,97 +432,82 @@
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FFD1D9E6"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF424242"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
       <color rgb="FF1B2A4A"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF616161"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1565C0"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF9E9E9E"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F7A1F"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -664,9 +640,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -677,6 +650,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -825,7 +801,11 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1B2A4A"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Targets by Geography</a:t>
             </a:r>
           </a:p>
@@ -857,6 +837,40 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B203-466A-8B1C-EE42834F3BD9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B203-466A-8B1C-EE42834F3BD9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -878,16 +892,13 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$A$12:$A$14</c:f>
+              <c:f>Dashboard!$A$12:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Florida</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FL</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>Unknown</c:v>
                 </c:pt>
               </c:strCache>
@@ -895,17 +906,14 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$B$12:$B$14</c:f>
+              <c:f>Dashboard!$B$12:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -913,7 +921,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8D8C-4D4E-A8C9-3C8BDA8D716E}"/>
+              <c16:uniqueId val="{00000004-B203-466A-8B1C-EE42834F3BD9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -930,13 +938,19 @@
       </c:pieChart>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="1"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -950,7 +964,7 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="10"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -962,8 +976,12 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Seller Readiness Score Distribution (# of Targets)</a:t>
+              <a:rPr lang="en-IN" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1B2A4A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Seller Readiness Score Distribution</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -972,7 +990,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0"/>
+          <c:y val="3.9197530864197534E-2"/>
+          <c:w val="0.91830409356725151"/>
+          <c:h val="0.91376543209876548"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -992,6 +1020,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1060,8 +1091,20 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E67A-4885-B986-A943DE1AEA96}"/>
+              <c16:uniqueId val="{00000000-D9B5-45BA-BF1E-E2C2A66E236D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1073,7 +1116,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="1"/>
         </c:dLbls>
-        <c:gapWidth val="50"/>
+        <c:gapWidth val="40"/>
         <c:axId val="10"/>
         <c:axId val="100"/>
       </c:barChart>
@@ -1082,8 +1125,26 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Readiness Score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1100,8 +1161,26 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t># of Targets</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1115,6 +1194,12 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1128,7 +1213,7 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="11"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1140,7 +1225,11 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1B2A4A"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Industry Breakdown</a:t>
             </a:r>
           </a:p>
@@ -1170,6 +1259,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D8E"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1244,8 +1336,20 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A61F-4240-AF74-01CB06097E60}"/>
+              <c16:uniqueId val="{00000000-73B8-41AA-A00F-D564F51CE99E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1266,8 +1370,26 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t># of Targets</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1284,7 +1406,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1299,6 +1421,12 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1316,7 +1444,7 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3780000" cy="3240000"/>
+    <xdr:ext cx="3420000" cy="3240000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -1347,7 +1475,7 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3780000" cy="3240000"/>
+    <xdr:ext cx="3420000" cy="3240000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
@@ -1373,12 +1501,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3600000" cy="3240000"/>
+    <xdr:ext cx="3780000" cy="3240000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">
@@ -1690,7 +1818,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L37"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1699,10 +1830,11 @@
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="20" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="45" customWidth="1"/>
+    <col min="12" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
@@ -1825,7 +1957,7 @@
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="47">
@@ -1907,43 +2039,43 @@
     </row>
     <row r="12" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" s="3">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="3">
         <v>1</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L12" s="28"/>
     </row>
     <row r="13" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -1952,55 +2084,47 @@
       <c r="L13" s="28"/>
     </row>
     <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="3">
-        <v>1</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="K14" s="27" t="s">
-        <v>35</v>
-      </c>
+      <c r="K14" s="28"/>
       <c r="L14" s="28"/>
     </row>
     <row r="15" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
       </c>
-      <c r="K15" s="28"/>
+      <c r="K15" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="L15" s="28"/>
     </row>
     <row r="16" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G16" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
       </c>
-      <c r="K16" s="27" t="s">
-        <v>39</v>
-      </c>
+      <c r="K16" s="28"/>
       <c r="L16" s="28"/>
     </row>
     <row r="17" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -2009,7 +2133,7 @@
     </row>
     <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K18" s="27" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L18" s="28"/>
     </row>
@@ -2018,13 +2142,13 @@
       <c r="L19" s="28"/>
     </row>
     <row r="20" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K20" s="27" t="s">
-        <v>41</v>
-      </c>
+      <c r="K20" s="28"/>
       <c r="L20" s="28"/>
     </row>
     <row r="21" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K21" s="28"/>
+      <c r="K21" s="27" t="s">
+        <v>38</v>
+      </c>
       <c r="L21" s="28"/>
     </row>
     <row r="22" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -2036,373 +2160,378 @@
       <c r="L23" s="28"/>
     </row>
     <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K24" s="28"/>
+      <c r="K24" s="27" t="s">
+        <v>39</v>
+      </c>
       <c r="L24" s="28"/>
     </row>
     <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K25" s="28"/>
       <c r="L25" s="28"/>
     </row>
-    <row r="28" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+    <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="30" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="F30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="I30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="J30" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="K30" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="26" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
-        <v>1</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="8">
-        <v>46</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" s="9">
-        <v>60</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="52" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
-        <v>2</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="8">
-        <v>28</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="9">
-        <v>45</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="26" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="8">
-        <v>99</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="12">
-        <v>35</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>64</v>
+        <v>51</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="8">
+        <v>60</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="26" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
+        <v>2</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="7">
+        <v>28</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="G32" s="8">
+        <v>45</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>3</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="7">
+        <v>99</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="12">
+        <v>35</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>4</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" s="12">
+        <v>35</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="6" t="s">
+    </row>
+    <row r="35" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>5</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="8">
-        <v>46</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G32" s="12">
-        <v>35</v>
-      </c>
-      <c r="H32" s="7" t="s">
+      <c r="C35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="12">
+        <v>25</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J32" s="6" t="s">
+    </row>
+    <row r="36" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
+        <v>6</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
-        <v>5</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="D36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" s="12">
+        <v>25</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="8">
+    </row>
+    <row r="37" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
+        <v>7</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="7">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" s="12">
+        <v>10</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A38" s="5">
+        <v>8</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="7">
+        <v>9</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="12">
         <v>0</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" s="12">
-        <v>25</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
+        <v>9</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="7">
         <v>6</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="12">
-        <v>25</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
-        <v>7</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="8">
-        <v>10</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="12">
-        <v>10</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
-        <v>8</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="F39" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="12">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="8">
-        <v>9</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G36" s="12">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="26" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
-        <v>9</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" s="8">
-        <v>6</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="12">
-        <v>0</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A28:J28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A30:K30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="35">
-    <mergeCell ref="K20:L25"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="K24:L27"/>
     <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E7:G7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="K21:L23"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K12:L14"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="K15:L17"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K18:L20"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2427,7 +2556,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>20</v>
@@ -2436,75 +2565,75 @@
         <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F2" s="15">
         <v>46</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K2" s="16">
         <v>60</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M2" s="17">
         <v>46195</v>
@@ -2515,40 +2644,40 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="F3" s="15">
         <v>28</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K3" s="16">
         <v>45</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M3" s="17">
         <v>46195</v>
@@ -2559,40 +2688,40 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F4" s="15">
         <v>99</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K4" s="18">
         <v>35</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M4" s="17">
         <v>46194</v>
@@ -2603,40 +2732,40 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F5" s="15">
         <v>46</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K5" s="18">
         <v>35</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M5" s="17">
         <v>46194</v>
@@ -2647,40 +2776,40 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="15">
         <v>0</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K6" s="18">
         <v>25</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M6" s="17">
         <v>46194</v>
@@ -2691,40 +2820,40 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F7" s="15">
         <v>3</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K7" s="18">
         <v>25</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M7" s="17">
         <v>46194</v>
@@ -2735,40 +2864,40 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F8" s="15">
         <v>10</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K8" s="18">
         <v>10</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M8" s="17">
         <v>46194</v>
@@ -2779,40 +2908,40 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F9" s="15">
         <v>9</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K9" s="18">
         <v>0</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M9" s="17">
         <v>46194</v>
@@ -2823,40 +2952,40 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F10" s="15">
         <v>6</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K10" s="18">
         <v>0</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M10" s="17">
         <v>46194</v>
@@ -2888,34 +3017,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.35">
@@ -2923,25 +3052,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="21">
         <v>60</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I2" s="20"/>
       <c r="J2" s="20">
@@ -2953,25 +3082,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="21">
         <v>45</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="20">
@@ -2983,25 +3112,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" s="22">
         <v>35</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I4" s="20"/>
       <c r="J4" s="20">
@@ -3013,25 +3142,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" s="22">
         <v>35</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I5" s="20"/>
       <c r="J5" s="20">
@@ -3043,25 +3172,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" s="22">
         <v>25</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20">
@@ -3073,25 +3202,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C7" s="22">
         <v>25</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I7" s="20"/>
       <c r="J7" s="20">
@@ -3103,25 +3232,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" s="22">
         <v>10</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I8" s="20"/>
       <c r="J8" s="20">
@@ -3133,25 +3262,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C9" s="22">
         <v>0</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I9" s="20"/>
       <c r="J9" s="20">
@@ -3163,25 +3292,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C10" s="22">
         <v>0</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I10" s="20"/>
       <c r="J10" s="20">
